--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -604,10 +604,10 @@
         <v>718</v>
       </c>
       <c r="K3" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="L3" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M3" t="n">
         <v>1289</v>
@@ -616,7 +616,7 @@
         <v>218</v>
       </c>
       <c r="O3" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P3" t="n">
         <v>207</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="D13" t="n">
         <v>304</v>

--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -1139,7 +1139,7 @@
         <v>849</v>
       </c>
       <c r="F13" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G13" t="n">
         <v>2183</v>

--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -604,10 +604,10 @@
         <v>718</v>
       </c>
       <c r="K3" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="L3" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="M3" t="n">
         <v>1289</v>
@@ -616,7 +616,7 @@
         <v>218</v>
       </c>
       <c r="O3" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P3" t="n">
         <v>207</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="D13" t="n">
         <v>304</v>
@@ -1139,7 +1139,7 @@
         <v>849</v>
       </c>
       <c r="F13" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G13" t="n">
         <v>2183</v>

--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -604,19 +604,19 @@
         <v>718</v>
       </c>
       <c r="K3" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="L3" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M3" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N3" t="n">
         <v>218</v>
       </c>
       <c r="O3" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P3" t="n">
         <v>207</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="D13" t="n">
         <v>304</v>
@@ -1139,7 +1139,7 @@
         <v>849</v>
       </c>
       <c r="F13" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G13" t="n">
         <v>2183</v>

--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -601,16 +601,16 @@
         <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K3" t="n">
-        <v>2145</v>
+        <v>2149</v>
       </c>
       <c r="L3" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M3" t="n">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="N3" t="n">
         <v>218</v>
@@ -1130,22 +1130,22 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2726</v>
+        <v>2730</v>
       </c>
       <c r="D13" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E13" t="n">
         <v>849</v>
       </c>
       <c r="F13" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G13" t="n">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="H13" t="n">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">

--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -601,10 +601,10 @@
         <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="K3" t="n">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="L3" t="n">
         <v>603</v>
@@ -1130,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2730</v>
+        <v>2735</v>
       </c>
       <c r="D13" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E13" t="n">
         <v>849</v>
@@ -1145,7 +1145,7 @@
         <v>2184</v>
       </c>
       <c r="H13" t="n">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29">

--- a/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
+++ b/aircraft/reports/manufacturer-aircraft-heatmap.xlsx
@@ -604,19 +604,19 @@
         <v>720</v>
       </c>
       <c r="K3" t="n">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="L3" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M3" t="n">
         <v>1292</v>
       </c>
       <c r="N3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O3" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P3" t="n">
         <v>207</v>
@@ -1130,22 +1130,22 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2735</v>
+        <v>2737</v>
       </c>
       <c r="D13" t="n">
         <v>306</v>
       </c>
       <c r="E13" t="n">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="F13" t="n">
         <v>549</v>
       </c>
       <c r="G13" t="n">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="H13" t="n">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
